--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:05</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:14</t>
+    <t xml:space="preserve">2026-10-05 10:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -605,7 +605,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1100493.62</v>
+        <v>1100493.63</v>
       </c>
     </row>
     <row r="5">
@@ -656,7 +656,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1054870.62</v>
+        <v>1054870.63</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1031225.62</v>
+        <v>1031225.63</v>
       </c>
     </row>
     <row r="9">
@@ -758,7 +758,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1013836.12</v>
+        <v>1013836.13</v>
       </c>
     </row>
     <row r="14">
@@ -826,7 +826,7 @@
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>991847.12</v>
+        <v>991847.13</v>
       </c>
     </row>
     <row r="18">
@@ -911,7 +911,7 @@
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>945811.12</v>
+        <v>945811.13</v>
       </c>
     </row>
     <row r="23">
@@ -1013,7 +1013,7 @@
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>879298.62</v>
+        <v>879298.63</v>
       </c>
     </row>
     <row r="29">
@@ -1030,7 +1030,7 @@
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>873026.62</v>
+        <v>873026.63</v>
       </c>
     </row>
     <row r="30">
